--- a/tests/QA_2/Q_related-FUSE_FINA.xlsx
+++ b/tests/QA_2/Q_related-FUSE_FINA.xlsx
@@ -217,7 +217,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
   <si>
-    <t>答案</t>
+    <t>问题</t>
   </si>
   <si>
     <t>标准答案</t>
